--- a/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
+++ b/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\backend\data_wizard\tests\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\product-docs\.gitbook\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4594D145-2EA5-4136-8421-0A8AC7FB8944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F05CB7-C0F3-4439-B3AC-E28A7E3FBBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4536" yWindow="2028" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
   <si>
     <t>ref_id</t>
   </si>
@@ -257,6 +257,24 @@
   </si>
   <si>
     <t>Compliance Manager</t>
+  </si>
+  <si>
+    <t>alexandre.morel@acmecorp.com</t>
+  </si>
+  <si>
+    <t>Alexandre</t>
+  </si>
+  <si>
+    <t>Morel</t>
+  </si>
+  <si>
+    <t>Primary operational contact for ACME Corporation security coordination</t>
+  </si>
+  <si>
+    <t>+33 1 42 00 00 03</t>
+  </si>
+  <si>
+    <t>Security Coordinator</t>
   </si>
 </sst>
 </file>
@@ -314,12 +332,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -996,13 +1015,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C56EDC4-5FDC-4B05-889D-1A302F57D200}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" customWidth="1"/>
-    <col min="4" max="4" width="44.109375" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1033,22 +1052,22 @@
       <c r="A2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1056,22 +1075,45 @@
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1079,8 +1121,9 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{7EC3EECF-D9E2-4361-AFAC-CAD1CE346FB9}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{B5BC6947-747D-4BFB-8830-F6C14A7D7631}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{E7632B3E-F078-475A-8F2A-9BF8F35D95C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
+++ b/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\product-docs\.gitbook\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F05CB7-C0F3-4439-B3AC-E28A7E3FBBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75431463-6B77-4A0D-BA36-D11CF9755F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4536" yWindow="2028" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="-11160" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
     <sheet name="Solutions" sheetId="2" r:id="rId2"/>
     <sheet name="Contracts" sheetId="3" r:id="rId3"/>
-    <sheet name=" Representatives" sheetId="4" r:id="rId4"/>
+    <sheet name="Representatives" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
+++ b/product-docs/.gitbook/assets/third_parties_ecosystem_template.xlsx
@@ -84,7 +84,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -93,11 +93,11 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+  </cellStyleXfs>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,21 +126,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="6" builtinId="8"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -386,180 +385,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.78125" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="6" min="1" max="1"/>
-    <col width="19" customWidth="1" style="6" min="2" max="2"/>
-    <col width="24" customWidth="1" style="6" min="3" max="3"/>
-    <col width="29" customWidth="1" style="6" min="4" max="4"/>
-    <col width="10" customWidth="1" style="6" min="5" max="5"/>
-    <col width="11" customWidth="1" style="6" min="6" max="6"/>
-    <col width="23" customWidth="1" style="6" min="7" max="7"/>
-    <col width="17.33" customWidth="1" style="6" min="8" max="8"/>
-    <col width="10.44" customWidth="1" style="6" min="9" max="9"/>
+    <col width="10" customWidth="1" style="7" min="1" max="1"/>
+    <col width="19" customWidth="1" style="7" min="2" max="2"/>
+    <col width="24" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29" customWidth="1" style="7" min="4" max="4"/>
+    <col width="10" customWidth="1" style="7" min="5" max="5"/>
+    <col width="11" customWidth="1" style="7" min="6" max="6"/>
+    <col width="23" customWidth="1" style="7" min="7" max="7"/>
+    <col width="17.33" customWidth="1" style="7" min="8" max="8"/>
+    <col width="10.44" customWidth="1" style="7" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="14.25" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ref_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>parent_entity_ref_id</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>dependency</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>penetration</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>maturity</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>trust</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>ACME Corporation</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Cool organisation</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Provide excellent services</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="14.25" customHeight="1" s="8">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ENT-002</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>ACME Europe</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>European branch</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>European operations</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="7">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="14.25" customHeight="1" s="8">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>TechVendor Inc</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>External ICT provider</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Cloud services provider</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" s="8">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Nameless Ventures</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Newly onboarded vendor, ref_id not assigned yet</t>
         </is>
       </c>
     </row>
@@ -576,116 +587,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.78125" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="6" min="1" max="1"/>
-    <col width="24" customWidth="1" style="6" min="2" max="2"/>
-    <col width="42" customWidth="1" style="6" min="3" max="3"/>
-    <col width="25" customWidth="1" style="6" min="4" max="4"/>
-    <col width="14" customWidth="1" style="6" min="5" max="5"/>
+    <col width="10" customWidth="1" style="7" min="1" max="1"/>
+    <col width="24" customWidth="1" style="7" min="2" max="2"/>
+    <col width="42" customWidth="1" style="7" min="3" max="3"/>
+    <col width="25" customWidth="1" style="7" min="4" max="4"/>
+    <col width="14" customWidth="1" style="7" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="14.25" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ref_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>provider_entity_ref_id</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>provider_entity_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>SOL-001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Cloud Storage Service</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Enterprise cloud storage solution</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="14.25" customHeight="1" s="8">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>SOL-002</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Email Service</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Corporate email platform</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="7">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="14.25" customHeight="1" s="8">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>SOL-003</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Internal CRM</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Customer relationship management system</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" s="8">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>SOL-004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Nameless Onboarding Service</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Pilot service from a newly onboarded vendor</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Nameless Ventures</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -704,157 +745,156 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20.22" customWidth="1" style="6" min="2" max="2"/>
-    <col width="14.09" customWidth="1" style="6" min="8" max="8"/>
-    <col width="35.66" customWidth="1" style="6" min="9" max="9"/>
-    <col width="20.59" customWidth="1" style="6" min="10" max="10"/>
+    <col width="20.22" customWidth="1" style="7" min="2" max="2"/>
+    <col width="14.09" customWidth="1" style="7" min="8" max="8"/>
+    <col width="35.66" customWidth="1" style="7" min="9" max="9"/>
+    <col width="20.59" customWidth="1" style="7" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="7">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="8">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>entity_ref_id</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>solution_ref_id</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>audit_ref_id</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>audit_name</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.4" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>TechVendor Annual Security Review</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Yearly security assessment of our cloud storage provider</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>SOL-001</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ISO 27002 SOA</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="16.4" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="J2" s="10" t="n"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="8">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>ACME Internal Controls Review</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Review of ACME Corporation internal controls</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>GDPR review for HR platform</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.4" customHeight="1" s="7">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="8">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ENT-002</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>ACME Controls Review</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Review of ACME Corporation internal controls</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="6" t="n"/>
+      <c r="I4" s="10" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -880,239 +920,239 @@
   <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.78125" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="6" min="1" max="1"/>
-    <col width="25" customWidth="1" style="6" min="2" max="2"/>
-    <col width="37" customWidth="1" style="6" min="3" max="3"/>
-    <col width="25" customWidth="1" style="6" min="4" max="4"/>
-    <col width="18" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9" customWidth="1" style="6" min="6" max="6"/>
-    <col width="13" customWidth="1" style="6" min="7" max="8"/>
-    <col width="17" customWidth="1" style="6" min="9" max="9"/>
-    <col width="11" customWidth="1" style="6" min="10" max="10"/>
+    <col width="10" customWidth="1" style="7" min="1" max="1"/>
+    <col width="25" customWidth="1" style="7" min="2" max="2"/>
+    <col width="37" customWidth="1" style="7" min="3" max="3"/>
+    <col width="25" customWidth="1" style="7" min="4" max="4"/>
+    <col width="18" customWidth="1" style="7" min="5" max="5"/>
+    <col width="9" customWidth="1" style="7" min="6" max="6"/>
+    <col width="13" customWidth="1" style="7" min="7" max="8"/>
+    <col width="17" customWidth="1" style="7" min="9" max="9"/>
+    <col width="11" customWidth="1" style="7" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="14.25" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ref_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>provider_entity_ref_id</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>solution_ref_id</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>annual_expense</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>lei</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>euid</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>vat</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>duns</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>CON-001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Cloud Storage Contract</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Annual cloud storage agreement</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>SOL-001</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="7" t="n">
         <v>50000</v>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="14.25" customHeight="1" s="8">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>CON-002</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Email Services SLA</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Service level agreement for email</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>SOL-002</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>75000</v>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="7">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="14.25" customHeight="1" s="8">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>CON-003</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>CRM Maintenance</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Internal CRM maintenance agreement</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>SOL-003</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>25000</v>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -1134,156 +1174,156 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.59765625" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="6" min="1" max="1"/>
-    <col width="63.22" customWidth="1" style="6" min="4" max="4"/>
-    <col width="18.67" customWidth="1" style="6" min="5" max="5"/>
-    <col width="19" customWidth="1" style="6" min="6" max="6"/>
-    <col width="21.66" customWidth="1" style="6" min="7" max="7"/>
+    <col width="30" customWidth="1" style="7" min="1" max="1"/>
+    <col width="63.22" customWidth="1" style="7" min="4" max="4"/>
+    <col width="18.67" customWidth="1" style="7" min="5" max="5"/>
+    <col width="19" customWidth="1" style="7" min="6" max="6"/>
+    <col width="21.66" customWidth="1" style="7" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="14.25" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>provider_entity_ref_id</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.4" customHeight="1" s="7">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="8">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>marie.durand@techvendor.com</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Marie</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>Durand</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Main security contact for vendor communications</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>+33 1 42 00 00 01</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>CISO</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>ENT-003</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16.4" customHeight="1" s="7">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="8">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>thomas.leroy@acmecorp.com</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Leroy</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Administrative and contract management contact</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>+33 1 42 00 00 02</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Compliance Manager</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.4" customHeight="1" s="7">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="8">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>alexandre.morel@acmecorp.com</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Alexandre</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Morel</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Primary operational contact for ACME Corporation security coordination</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>+33 1 42 00 00 03</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Security Coordinator</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>ENT-001</t>
         </is>
